--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6180,8 +6310,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -6204,1542 +6338,1763 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오봉산 타령 — 민요채보-3/오봉산 타령.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">오봉산 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">담</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">벙</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="19"/>
+      <c r="T4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="20"/>
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="20"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="20"/>
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="20"/>
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="20"/>
+      <c r="P5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="Q5" s="20"/>
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="S5" s="20"/>
+      <c r="T5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">논</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="L6" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="19"/>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="19"/>
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="19"/>
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="19"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K7" s="19"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="19"/>
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q7" s="19"/>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="20"/>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="20"/>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="20"/>
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="20"/>
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="20"/>
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="Q8" s="20"/>
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="S8" s="20"/>
+      <c r="T8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="18"/>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="19"/>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="19"/>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="19"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="19"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="19"/>
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="19"/>
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="19"/>
+      <c r="P10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q10" s="19"/>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S10" s="19"/>
+      <c r="T10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C11" s="20"/>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="20"/>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="20"/>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="20"/>
+      <c r="P11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="20"/>
+      <c r="R11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="S11" s="20"/>
+      <c r="T11" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="18"/>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G12" s="18"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 林</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="18"/>
+      <c r="P12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="E13" s="19"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="19"/>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="M13" s="19"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="19"/>
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="Q13" s="19"/>
+      <c r="R13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="S13" s="19"/>
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="U13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="20"/>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="20"/>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 林</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K14" s="20"/>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="20"/>
+      <c r="P14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q14" s="20"/>
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="S14" s="20"/>
+      <c r="T14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오봉산 타령 — 민요채보-3/오봉산 타령.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U14" s="20"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">오봉산 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="Q17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">알</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="R17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="T17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="U17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="17"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="S18" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">송</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="T18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="U18" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q19" s="20"/>
+      <c r="R19" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S19" s="20"/>
+      <c r="T19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 淋</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U19" s="20"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="Q20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="R20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="S20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="T20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="U20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="17"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="Q21" s="19"/>
+      <c r="R21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="S21" s="19"/>
+      <c r="T21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 淋</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="U21" s="19"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="Q22" s="20"/>
+      <c r="R22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="S22" s="20"/>
+      <c r="T22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 姑</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U22" s="20"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="Q23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="R23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="S23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="T23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="U23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="17"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="Q24" s="19"/>
+      <c r="R24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="S24" s="19"/>
+      <c r="T24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="U24" s="19"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="S25" s="20"/>
+      <c r="T25" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="U25" s="20"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="Q26" s="18"/>
+      <c r="R26" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="S26" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="T26" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="17"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="S27" s="19"/>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U27" s="19"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="Q28" s="20"/>
+      <c r="R28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="S28" s="20"/>
+      <c r="T28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
+      <c r="U28" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -931,12 +931,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2668,7 +2668,7 @@
       <c r="I58" s="3"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">짧은 점(―일 수도)</t>
+          <t xml:space="preserve">짧은 점(–일 수도)</t>
         </is>
       </c>
       <c r="K58" s="2"/>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I76" s="2"/>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I88" s="2"/>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I90" s="2"/>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="I106" s="2"/>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I112" s="2"/>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I114" s="2"/>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="I130" s="2"/>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I132" s="2"/>
@@ -5588,12 +5588,12 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I136" s="2"/>
@@ -5662,12 +5662,12 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I138" s="2"/>
@@ -6032,12 +6032,12 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="I154" s="2"/>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|○</t>
+          <t xml:space="preserve">–|○</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -6493,12 +6493,12 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I160" s="2"/>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="I162" s="2"/>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I180" s="2"/>
@@ -7575,13 +7575,13 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -7591,19 +7591,19 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="Q5" s="10"/>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="T5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="U5" s="10"/>
@@ -7757,7 +7757,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="C7" s="9"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="G7" s="9"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="10"/>
@@ -7902,7 +7902,7 @@
       <c r="O8" s="10"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="10"/>
@@ -7914,7 +7914,7 @@
       <c r="S8" s="10"/>
       <c r="T8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="10"/>
@@ -8127,7 +8127,7 @@
       <c r="C11" s="10"/>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="E11" s="10"/>
@@ -8301,43 +8301,43 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="9"/>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S13" s="9"/>
       <c r="T13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋</t>
+          <t xml:space="preserve">–淋</t>
         </is>
       </c>
       <c r="U13" s="9"/>
@@ -8346,7 +8346,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -8576,7 +8576,7 @@
       <c r="K19" s="10"/>
       <c r="L19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -8586,13 +8586,13 @@
       </c>
       <c r="N19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -8602,13 +8602,13 @@
       </c>
       <c r="R19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S19" s="10"/>
       <c r="T19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="U19" s="10" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="N21" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="O21" s="9"/>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰</t>
+          <t xml:space="preserve">–汰</t>
         </is>
       </c>
       <c r="S21" s="9"/>
@@ -8934,7 +8934,7 @@
       <c r="K25" s="10"/>
       <c r="L25" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="P25" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="Q25" s="10"/>
@@ -8966,7 +8966,7 @@
       <c r="S25" s="10"/>
       <c r="T25" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林</t>
+          <t xml:space="preserve">–林</t>
         </is>
       </c>
       <c r="U25" s="10"/>
@@ -9048,7 +9048,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M27" s="9"/>
@@ -9072,7 +9072,7 @@
       <c r="S27" s="9"/>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U27" s="9"/>
@@ -9103,7 +9103,7 @@
       <c r="O28" s="10"/>
       <c r="P28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7344,129 +7385,129 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">오봉산 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
@@ -7474,98 +7515,98 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">송</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
@@ -7573,181 +7614,181 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="24"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">김</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
@@ -7755,90 +7796,90 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">슴</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
@@ -7846,173 +7887,173 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="24"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="O8" s="24"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="Q8" s="24"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="S8" s="24"/>
+      <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꺾</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
@@ -8020,98 +8061,98 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
+      <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="U10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -8119,161 +8160,161 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="28"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="24"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="S11" s="24"/>
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="U11" s="10"/>
+      <c r="U11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="T12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -8281,219 +8322,219 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="23"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="Q13" s="23"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17" t="inlineStr">
+      <c r="S13" s="23"/>
+      <c r="T13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="U13" s="9"/>
+      <c r="U13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="24"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="24"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="24"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17" t="inlineStr">
+      <c r="S14" s="24"/>
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="U14" s="10"/>
+      <c r="U14" s="24"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">오봉산 타령</t>
         </is>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr">
+      <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R17" s="17" t="inlineStr">
+      <c r="R17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="S17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
       </c>
-      <c r="T17" s="17" t="inlineStr">
+      <c r="T17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="U17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8501,62 +8542,62 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr">
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O18" s="9" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="P18" s="17" t="inlineStr">
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q18" s="9" t="inlineStr">
+      <c r="Q18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
       </c>
-      <c r="R18" s="17" t="inlineStr">
+      <c r="R18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S18" s="9" t="inlineStr">
+      <c r="S18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">발</t>
         </is>
       </c>
-      <c r="T18" s="17" t="inlineStr">
+      <c r="T18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U18" s="9" t="inlineStr">
+      <c r="U18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -8564,54 +8605,54 @@
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="0"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="17" t="inlineStr">
+      <c r="B19" s="21"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
+      <c r="M19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr">
+      <c r="N19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="17" t="inlineStr">
+      <c r="O19" s="24"/>
+      <c r="P19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q19" s="10" t="inlineStr">
+      <c r="Q19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="R19" s="17" t="inlineStr">
+      <c r="R19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S19" s="10"/>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="S19" s="24"/>
+      <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="U19" s="10" t="inlineStr">
+      <c r="U19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -8619,62 +8660,62 @@
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="0"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="17" t="inlineStr">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="P20" s="17" t="inlineStr">
+      <c r="P20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="R20" s="17" t="inlineStr">
+      <c r="R20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
       </c>
-      <c r="T20" s="17" t="inlineStr">
+      <c r="T20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="U20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -8682,54 +8723,54 @@
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="0"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="B21" s="21"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr">
+      <c r="N21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="O21" s="9"/>
-      <c r="P21" s="17" t="inlineStr">
+      <c r="O21" s="23"/>
+      <c r="P21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="Q21" s="9" t="inlineStr">
+      <c r="Q21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="R21" s="17" t="inlineStr">
+      <c r="R21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="S21" s="9"/>
-      <c r="T21" s="17" t="inlineStr">
+      <c r="S21" s="23"/>
+      <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
@@ -8737,58 +8778,58 @@
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="0"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="17" t="inlineStr">
+      <c r="B22" s="21"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="O22" s="10" t="inlineStr">
+      <c r="O22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="P22" s="18" t="inlineStr">
+      <c r="P22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q22" s="13" t="inlineStr">
+      <c r="Q22" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">간다</t>
         </is>
       </c>
-      <c r="R22" s="17" t="inlineStr">
+      <c r="R22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="S22" s="10"/>
-      <c r="T22" s="18" t="inlineStr">
+      <c r="S22" s="24"/>
+      <c r="T22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="U22" s="13" t="inlineStr">
+      <c r="U22" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -8796,62 +8837,62 @@
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="0"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="17" t="inlineStr">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr">
+      <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
+      <c r="P23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="R23" s="17" t="inlineStr">
+      <c r="R23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S23" s="8" t="inlineStr">
+      <c r="S23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
       </c>
-      <c r="T23" s="17" t="inlineStr">
+      <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="U23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -8859,62 +8900,62 @@
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="0"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="17" t="inlineStr">
+      <c r="B24" s="21"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr">
+      <c r="N24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O24" s="9" t="inlineStr">
+      <c r="O24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">잊</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
+      <c r="P24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q24" s="9" t="inlineStr">
+      <c r="Q24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="R24" s="17" t="inlineStr">
+      <c r="R24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S24" s="9" t="inlineStr">
+      <c r="S24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="T24" s="17" t="inlineStr">
+      <c r="T24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U24" s="9" t="inlineStr">
+      <c r="U24" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
@@ -8922,113 +8963,113 @@
     </row>
     <row r="25" ht="56" customHeight="1">
       <c r="A25" s="0"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="17" t="inlineStr">
+      <c r="B25" s="21"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr">
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
+      <c r="O25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
+      <c r="P25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="17" t="inlineStr">
+      <c r="Q25" s="24"/>
+      <c r="R25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="S25" s="10"/>
-      <c r="T25" s="17" t="inlineStr">
+      <c r="S25" s="24"/>
+      <c r="T25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="U25" s="10"/>
+      <c r="U25" s="24"/>
     </row>
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="0"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="17" t="inlineStr">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="P26" s="17" t="inlineStr">
+      <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="R26" s="17" t="inlineStr">
+      <c r="R26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="T26" s="17" t="inlineStr">
+      <c r="T26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="U26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -9036,90 +9077,90 @@
     </row>
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="0"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="B27" s="21"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="17" t="inlineStr">
+      <c r="M27" s="23"/>
+      <c r="N27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O27" s="9"/>
-      <c r="P27" s="17" t="inlineStr">
+      <c r="O27" s="23"/>
+      <c r="P27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="17" t="inlineStr">
+      <c r="Q27" s="23"/>
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S27" s="9"/>
-      <c r="T27" s="17" t="inlineStr">
+      <c r="S27" s="23"/>
+      <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U27" s="9"/>
+      <c r="U27" s="23"/>
     </row>
     <row r="28" ht="56" customHeight="1">
       <c r="A28" s="0"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="18" t="inlineStr">
+      <c r="B28" s="21"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="M28" s="13"/>
-      <c r="N28" s="17" t="inlineStr">
+      <c r="M28" s="28"/>
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="17" t="inlineStr">
+      <c r="O28" s="24"/>
+      <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="17" t="inlineStr">
+      <c r="Q28" s="24"/>
+      <c r="R28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S28" s="10"/>
-      <c r="T28" s="17" t="inlineStr">
+      <c r="S28" s="24"/>
+      <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U28" s="10"/>
+      <c r="U28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -7358,32 +7358,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="28"/>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="28"/>
@@ -8450,7 +8450,7 @@
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="55.19" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -8658,7 +8658,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="55.19" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="55.19" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="55.19" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="55.19" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -8898,7 +8898,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="55.19" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="55.19" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="55.19" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9075,7 +9075,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="55.19" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="55.19" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -5055,13 +5055,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I121" s="2"/>
@@ -6420,13 +6419,12 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I157" s="2"/>
@@ -6873,12 +6871,12 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I169" s="2"/>
@@ -7333,12 +7331,12 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I181" s="3"/>
@@ -7383,7 +7381,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -7410,7 +7408,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7513,7 +7511,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7612,7 +7610,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7691,7 +7689,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="55.19" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7794,7 +7792,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -7885,7 +7883,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="55.19" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7960,7 +7958,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="55.19" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -8059,7 +8057,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -8158,7 +8156,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="55.19" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -8221,7 +8219,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="55.19" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -8320,7 +8318,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -8383,12 +8381,11 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -8450,7 +8447,7 @@
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="55.19" customHeight="1">
+    <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -8477,7 +8474,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="55.19" customHeight="1">
+    <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -8540,7 +8537,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="55.19" customHeight="1">
+    <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -8603,7 +8600,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="55.19" customHeight="1">
+    <row r="19" ht="29.14" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -8658,7 +8655,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="55.19" customHeight="1">
+    <row r="20" ht="29.14" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -8721,7 +8718,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="55.19" customHeight="1">
+    <row r="21" ht="29.14" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -8776,7 +8773,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="55.19" customHeight="1">
+    <row r="22" ht="29.14" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -8835,7 +8832,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="55.19" customHeight="1">
+    <row r="23" ht="29.14" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -8898,7 +8895,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="55.19" customHeight="1">
+    <row r="24" ht="29.14" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -8961,7 +8958,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="55.19" customHeight="1">
+    <row r="25" ht="29.14" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -9012,7 +9009,7 @@
       </c>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="55.19" customHeight="1">
+    <row r="26" ht="29.14" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9075,7 +9072,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="55.19" customHeight="1">
+    <row r="27" ht="29.14" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -9118,7 +9115,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="55.19" customHeight="1">
+    <row r="28" ht="29.14" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -9132,20 +9129,19 @@
       <c r="K28" s="24"/>
       <c r="L28" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M28" s="28"/>
       <c r="N28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O28" s="24"/>
       <c r="P28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q28" s="24"/>

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -8812,7 +8812,8 @@
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">간다</t>
+          <t xml:space="preserve">간
+다</t>
         </is>
       </c>
       <c r="R22" s="21" t="inlineStr">

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7415,7 +7438,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -7425,7 +7448,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -7435,7 +7458,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -7445,7 +7468,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -7455,7 +7478,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -7465,7 +7488,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -7475,7 +7498,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
@@ -7485,7 +7508,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -7495,7 +7518,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
@@ -7505,7 +7528,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U3" s="22" t="inlineStr">
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
@@ -7518,7 +7541,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -7528,7 +7551,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -7538,7 +7561,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
@@ -7548,7 +7571,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">송</t>
         </is>
@@ -7558,7 +7581,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -7568,13 +7591,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="30"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="O4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -7584,7 +7607,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q4" s="23" t="inlineStr">
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -7594,7 +7617,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S4" s="23" t="inlineStr">
+      <c r="S4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -7604,7 +7627,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U4" s="23" t="inlineStr">
+      <c r="U4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
@@ -7617,13 +7640,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -7633,19 +7656,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="24"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="K5" s="24" t="inlineStr">
+      <c r="K5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -7655,13 +7678,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="31"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="O5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -7671,13 +7694,13 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="Q5" s="24"/>
+      <c r="Q5" s="31"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S5" s="24" t="inlineStr">
+      <c r="S5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -7687,7 +7710,7 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="U5" s="24"/>
+      <c r="U5" s="31"/>
     </row>
     <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
@@ -7696,7 +7719,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -7706,7 +7729,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -7716,7 +7739,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -7726,7 +7749,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -7736,7 +7759,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -7746,7 +7769,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -7756,7 +7779,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">김</t>
         </is>
@@ -7766,7 +7789,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -7776,7 +7799,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
@@ -7786,7 +7809,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U6" s="22" t="inlineStr">
+      <c r="U6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
@@ -7799,13 +7822,13 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -7815,13 +7838,13 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -7831,7 +7854,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -7841,13 +7864,13 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="M7" s="23"/>
+      <c r="M7" s="30"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -7857,7 +7880,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="Q7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">슴</t>
         </is>
@@ -7867,7 +7890,7 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S7" s="23" t="inlineStr">
+      <c r="S7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
@@ -7877,7 +7900,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U7" s="23" t="inlineStr">
+      <c r="U7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
@@ -7890,7 +7913,7 @@
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -7900,19 +7923,19 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -7922,13 +7945,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="M8" s="24" t="inlineStr">
+      <c r="M8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -7938,25 +7961,25 @@
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="O8" s="24"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="24"/>
+      <c r="Q8" s="31"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑林</t>
         </is>
       </c>
-      <c r="S8" s="24"/>
+      <c r="S8" s="31"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="24"/>
+      <c r="U8" s="31"/>
     </row>
     <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
@@ -7965,7 +7988,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꺾</t>
         </is>
@@ -7975,13 +7998,13 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
@@ -7991,7 +8014,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -8001,7 +8024,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -8011,7 +8034,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -8021,7 +8044,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
@@ -8031,7 +8054,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
@@ -8041,7 +8064,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -8051,7 +8074,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
@@ -8064,7 +8087,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -8074,13 +8097,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -8090,7 +8113,7 @@
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -8100,7 +8123,7 @@
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -8110,7 +8133,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -8120,7 +8143,7 @@
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="O10" s="27" t="inlineStr">
+      <c r="O10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -8130,7 +8153,7 @@
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -8140,7 +8163,7 @@
           <t xml:space="preserve">南無</t>
         </is>
       </c>
-      <c r="S10" s="23" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -8150,7 +8173,7 @@
           <t xml:space="preserve">㴌淋</t>
         </is>
       </c>
-      <c r="U10" s="23" t="inlineStr">
+      <c r="U10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -8163,61 +8186,61 @@
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M11" s="28"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O11" s="24"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q11" s="24"/>
+      <c r="Q11" s="31"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S11" s="24"/>
+      <c r="S11" s="31"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="U11" s="24"/>
+      <c r="U11" s="31"/>
     </row>
     <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
@@ -8226,7 +8249,7 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -8236,13 +8259,13 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -8252,7 +8275,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -8262,7 +8285,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -8272,7 +8295,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -8282,7 +8305,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -8292,7 +8315,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -8302,7 +8325,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -8312,7 +8335,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="U12" s="22" t="inlineStr">
+      <c r="U12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -8325,61 +8348,61 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="30"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="30"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="30"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S13" s="23"/>
+      <c r="S13" s="30"/>
       <c r="T13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋</t>
         </is>
       </c>
-      <c r="U13" s="23"/>
+      <c r="U13" s="30"/>
     </row>
     <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
@@ -8388,61 +8411,61 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="24"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="24"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="24"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="24"/>
+      <c r="S14" s="31"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="U14" s="24"/>
+      <c r="U14" s="31"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
@@ -8477,21 +8500,21 @@
     <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="22"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="29"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
+      <c r="K17" s="29"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="M17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8501,7 +8524,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O17" s="22" t="inlineStr">
+      <c r="O17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -8511,7 +8534,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="inlineStr">
+      <c r="Q17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8521,7 +8544,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S17" s="22" t="inlineStr">
+      <c r="S17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">단</t>
         </is>
@@ -8531,7 +8554,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U17" s="22" t="inlineStr">
+      <c r="U17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -8540,21 +8563,21 @@
     <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="23"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="23"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="23"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="23"/>
+      <c r="I18" s="30"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="23"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
+      <c r="M18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -8564,7 +8587,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
@@ -8574,7 +8597,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q18" s="23" t="inlineStr">
+      <c r="Q18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -8584,7 +8607,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S18" s="23" t="inlineStr">
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">발</t>
         </is>
@@ -8594,7 +8617,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U18" s="23" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">루</t>
         </is>
@@ -8603,21 +8626,21 @@
     <row r="19" ht="29.14" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="24"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="24"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="24"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="31"/>
       <c r="J19" s="21"/>
-      <c r="K19" s="24"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="M19" s="24" t="inlineStr">
+      <c r="M19" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -8627,13 +8650,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O19" s="24"/>
+      <c r="O19" s="31"/>
       <c r="P19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="Q19" s="24" t="inlineStr">
+      <c r="Q19" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -8643,13 +8666,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S19" s="24"/>
+      <c r="S19" s="31"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="U19" s="24" t="inlineStr">
+      <c r="U19" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -8658,21 +8681,21 @@
     <row r="20" ht="29.14" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="21"/>
-      <c r="E20" s="22"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="22"/>
+      <c r="I20" s="29"/>
       <c r="J20" s="21"/>
-      <c r="K20" s="22"/>
+      <c r="K20" s="29"/>
       <c r="L20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M20" s="22" t="inlineStr">
+      <c r="M20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">갈</t>
         </is>
@@ -8682,7 +8705,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O20" s="22" t="inlineStr">
+      <c r="O20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -8692,7 +8715,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q20" s="22" t="inlineStr">
+      <c r="Q20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
@@ -8702,7 +8725,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="S20" s="22" t="inlineStr">
+      <c r="S20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">령</t>
         </is>
@@ -8712,7 +8735,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="U20" s="22" t="inlineStr">
+      <c r="U20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -8721,21 +8744,21 @@
     <row r="21" ht="29.14" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="23"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="21"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="23"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="21"/>
-      <c r="I21" s="23"/>
+      <c r="I21" s="30"/>
       <c r="J21" s="21"/>
-      <c r="K21" s="23"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="M21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -8745,13 +8768,13 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="O21" s="23"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無汰</t>
         </is>
       </c>
-      <c r="Q21" s="23" t="inlineStr">
+      <c r="Q21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -8761,13 +8784,13 @@
           <t xml:space="preserve">–汰</t>
         </is>
       </c>
-      <c r="S21" s="23"/>
+      <c r="S21" s="30"/>
       <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U21" s="23" t="inlineStr">
+      <c r="U21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">양</t>
         </is>
@@ -8776,21 +8799,21 @@
     <row r="22" ht="29.14" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="24"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="24"/>
+      <c r="E22" s="31"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="24"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="31"/>
       <c r="J22" s="21"/>
-      <c r="K22" s="24"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="M22" s="24" t="inlineStr">
+      <c r="M22" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -8800,7 +8823,7 @@
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="O22" s="24" t="inlineStr">
+      <c r="O22" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -8810,7 +8833,7 @@
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="Q22" s="28" t="inlineStr">
+      <c r="Q22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">간
 다</t>
@@ -8821,13 +8844,13 @@
           <t xml:space="preserve">㴌汰</t>
         </is>
       </c>
-      <c r="S22" s="24"/>
+      <c r="S22" s="31"/>
       <c r="T22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="U22" s="28" t="inlineStr">
+      <c r="U22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -8836,21 +8859,21 @@
     <row r="23" ht="29.14" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
-      <c r="C23" s="22"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="22"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
+      <c r="K23" s="29"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="M23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
@@ -8860,7 +8883,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O23" s="22" t="inlineStr">
+      <c r="O23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -8870,7 +8893,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q23" s="22" t="inlineStr">
+      <c r="Q23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -8880,7 +8903,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="S23" s="22" t="inlineStr">
+      <c r="S23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꼭</t>
         </is>
@@ -8890,7 +8913,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="U23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -8899,21 +8922,21 @@
     <row r="24" ht="29.14" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
-      <c r="C24" s="23"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="23"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="23"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="23"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr">
+      <c r="M24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -8923,7 +8946,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O24" s="23" t="inlineStr">
+      <c r="O24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">잊</t>
         </is>
@@ -8933,7 +8956,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q24" s="23" t="inlineStr">
+      <c r="Q24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
@@ -8943,7 +8966,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="S24" s="23" t="inlineStr">
+      <c r="S24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -8953,7 +8976,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U24" s="23" t="inlineStr">
+      <c r="U24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
@@ -8962,21 +8985,21 @@
     <row r="25" ht="29.14" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
-      <c r="C25" s="24"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="24"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="24"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="31"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="24"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="M25" s="24" t="inlineStr">
+      <c r="M25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -8986,7 +9009,7 @@
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="O25" s="24" t="inlineStr">
+      <c r="O25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -8996,38 +9019,38 @@
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="Q25" s="24"/>
+      <c r="Q25" s="31"/>
       <c r="R25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南</t>
         </is>
       </c>
-      <c r="S25" s="24"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林</t>
         </is>
       </c>
-      <c r="U25" s="24"/>
+      <c r="U25" s="31"/>
     </row>
     <row r="26" ht="29.14" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
-      <c r="C26" s="22"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="22"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="22"/>
+      <c r="G26" s="29"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="22"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M26" s="22" t="inlineStr">
+      <c r="M26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -9037,7 +9060,7 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="O26" s="22" t="inlineStr">
+      <c r="O26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -9047,7 +9070,7 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="inlineStr">
+      <c r="Q26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -9057,7 +9080,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="S26" s="22" t="inlineStr">
+      <c r="S26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -9067,7 +9090,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U26" s="22" t="inlineStr">
+      <c r="U26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -9076,88 +9099,88 @@
     <row r="27" ht="29.14" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
-      <c r="C27" s="23"/>
+      <c r="C27" s="30"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="23"/>
+      <c r="G27" s="30"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="23"/>
+      <c r="I27" s="30"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="23"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M27" s="23"/>
+      <c r="M27" s="30"/>
       <c r="N27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O27" s="23"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q27" s="23"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="S27" s="23"/>
+      <c r="S27" s="30"/>
       <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U27" s="23"/>
+      <c r="U27" s="30"/>
     </row>
     <row r="28" ht="29.14" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
-      <c r="C28" s="24"/>
+      <c r="C28" s="31"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="24"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="24"/>
+      <c r="G28" s="31"/>
       <c r="H28" s="21"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="31"/>
       <c r="J28" s="21"/>
-      <c r="K28" s="24"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="M28" s="28"/>
+      <c r="M28" s="34"/>
       <c r="N28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O28" s="24"/>
+      <c r="O28" s="31"/>
       <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q28" s="24"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S28" s="24"/>
+      <c r="S28" s="31"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U28" s="24"/>
+      <c r="U28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -1890,6 +1890,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1902,10 +1905,10 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="42.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1920,7 +1923,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="93.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1975,7 +1978,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="93.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2028,7 +2031,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="93.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2084,7 +2087,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="93.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2134,7 +2137,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="93.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2193,7 +2196,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="93.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2252,7 +2255,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="93.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2303,7 +2306,7 @@
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="93.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -2356,6 +2359,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="95"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/오봉산 타령.xlsx
+++ b/sheets/민요/검수/오봉산 타령.xlsx
@@ -1895,13 +1895,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
